--- a/product-definitions/spreadsheet/rain-lwc-velocity-reflectivity.xlsx
+++ b/product-definitions/spreadsheet/rain-lwc-velocity-reflectivity.xlsx
@@ -305,7 +305,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2254,7 +2254,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
         <v>21</v>
@@ -2286,7 +2286,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
         <v>24</v>
@@ -2318,7 +2318,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
         <v>34</v>
@@ -2350,7 +2350,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
         <v>27</v>
@@ -2382,7 +2382,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2410,7 +2410,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
@@ -2440,7 +2440,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -2472,7 +2472,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>14</v>
@@ -2504,7 +2504,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
         <v>2</v>
@@ -2536,7 +2536,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2568,7 +2568,7 @@
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2600,7 +2600,7 @@
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
         <v>18</v>
@@ -2632,7 +2632,7 @@
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
         <v>21</v>
@@ -2664,7 +2664,7 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
         <v>24</v>
@@ -2696,7 +2696,7 @@
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
         <v>34</v>
@@ -2728,7 +2728,7 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
         <v>27</v>
@@ -2760,7 +2760,7 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2788,7 +2788,7 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>39</v>
       </c>
@@ -2818,7 +2818,7 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
         <v>12</v>
@@ -2850,7 +2850,7 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
         <v>14</v>
@@ -2882,7 +2882,7 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
         <v>2</v>
@@ -2914,7 +2914,7 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -2946,7 +2946,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2978,7 +2978,7 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
         <v>18</v>
@@ -3010,7 +3010,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
         <v>21</v>
@@ -3042,7 +3042,7 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
         <v>24</v>
@@ -3074,7 +3074,7 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
         <v>34</v>
@@ -3106,7 +3106,7 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
         <v>27</v>
@@ -3138,7 +3138,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -3166,7 +3166,7 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>42</v>
       </c>
@@ -3196,7 +3196,7 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
         <v>12</v>
@@ -3228,7 +3228,7 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
         <v>14</v>
@@ -3260,7 +3260,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
         <v>2</v>
@@ -3292,7 +3292,7 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3324,7 +3324,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3356,7 +3356,7 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
         <v>18</v>
@@ -3388,7 +3388,7 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
         <v>21</v>
@@ -3420,7 +3420,7 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
         <v>24</v>
@@ -3452,7 +3452,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>34</v>
@@ -3484,7 +3484,7 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>27</v>
@@ -3516,7 +3516,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3544,7 +3544,7 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>45</v>
       </c>
@@ -3574,7 +3574,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
         <v>12</v>
@@ -3606,7 +3606,7 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
         <v>14</v>
@@ -3638,7 +3638,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>2</v>
@@ -3670,7 +3670,7 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -3702,7 +3702,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="2"/>
       <c r="B67" s="2" t="s">
         <v>16</v>
@@ -3734,7 +3734,7 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
         <v>18</v>
@@ -3766,7 +3766,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="2" t="s">
         <v>21</v>
@@ -3798,7 +3798,7 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
         <v>24</v>
@@ -3830,7 +3830,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="2" t="s">
         <v>34</v>
@@ -3862,7 +3862,7 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2" t="s">
         <v>27</v>
@@ -3894,7 +3894,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3922,7 +3922,7 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="2" t="s">
         <v>47</v>
       </c>
@@ -3952,7 +3952,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="2"/>
       <c r="B75" s="2" t="s">
         <v>12</v>
@@ -3984,7 +3984,7 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="2" t="s">
         <v>14</v>
@@ -4016,7 +4016,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="2"/>
       <c r="B77" s="2" t="s">
         <v>2</v>
@@ -4048,7 +4048,7 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="2"/>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4080,7 +4080,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="2"/>
       <c r="B79" s="2" t="s">
         <v>16</v>
@@ -4112,7 +4112,7 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
         <v>18</v>
@@ -4144,7 +4144,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
         <v>21</v>
@@ -4176,7 +4176,7 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
         <v>24</v>
@@ -4208,7 +4208,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="2"/>
       <c r="B83" s="2" t="s">
         <v>34</v>
@@ -4240,7 +4240,7 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="2"/>
       <c r="B84" s="2" t="s">
         <v>27</v>
@@ -4272,7 +4272,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -4300,7 +4300,7 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="2" t="s">
         <v>50</v>
       </c>
@@ -4330,7 +4330,7 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="2"/>
       <c r="B87" s="2" t="s">
         <v>12</v>
@@ -4362,7 +4362,7 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="2"/>
       <c r="B88" s="2" t="s">
         <v>14</v>
@@ -4394,7 +4394,7 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="2"/>
       <c r="B89" s="2" t="s">
         <v>2</v>
@@ -4426,7 +4426,7 @@
       <c r="Y89" s="2"/>
       <c r="Z89" s="2"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="2"/>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -4456,7 +4456,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="2"/>
       <c r="B91" s="2" t="s">
         <v>16</v>
@@ -4488,7 +4488,7 @@
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="2"/>
       <c r="B92" s="8" t="s">
         <v>53</v>
@@ -4520,7 +4520,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="2"/>
       <c r="B93" s="17" t="s">
         <v>55</v>
